--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeExportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeExportError.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <r>
       <rPr>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -134,6 +140,42 @@
   </si>
   <si>
     <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.reportMonthStr}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.businessCode}</t>
+  </si>
+  <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.feeTypeName}</t>
+  </si>
+  <si>
+    <t>{.midPeriodTransitCostStr}</t>
+  </si>
+  <si>
+    <t>{.currentPeriodAllocatedCostStr}</t>
+  </si>
+  <si>
+    <t>{.endPeriodTransitCostStr}</t>
+  </si>
+  <si>
+    <t>{.endPeriodEstimatedCostStr}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
@@ -1124,8 +1166,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
@@ -1177,6 +1219,44 @@
       </c>
       <c r="L1" s="7" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeExportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeExportError.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <r>
       <rPr>
@@ -109,6 +109,19 @@
   </si>
   <si>
     <r>
+      <t>分摊重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(KG)</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
@@ -139,6 +152,9 @@
     <t>期末暂估费用(¥)</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -160,6 +176,9 @@
     <t>{.skuNo}</t>
   </si>
   <si>
+    <t>{.allocatedWeightStr}</t>
+  </si>
+  <si>
     <t>{.feeTypeName}</t>
   </si>
   <si>
@@ -173,6 +192,9 @@
   </si>
   <si>
     <t>{.endPeriodEstimatedCostStr}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -221,6 +243,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -368,11 +395,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -700,137 +722,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,10 +871,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1166,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.5" style="2" customWidth="1"/>
@@ -1174,16 +1199,17 @@
     <col min="3" max="3" width="20.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="17.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="26.875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="6" max="8" width="17.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14" style="2" customWidth="1"/>
+    <col min="14" max="14" width="26.875" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1202,61 +1228,73 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
